--- a/otimizacao/data/itens_cardapio.xlsx
+++ b/otimizacao/data/itens_cardapio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sofia\projeto-ru\otimizacao\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D50171-7EB3-4A33-8391-8BF9237BE9F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00F26F99-BEF9-4AFE-8A5B-AF166240F726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B19D17F5-DA6C-47BD-AE69-96B8880CAEEE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="209">
   <si>
     <t>item</t>
   </si>
@@ -642,6 +642,27 @@
   </si>
   <si>
     <t>tangerina</t>
+  </si>
+  <si>
+    <t>produto</t>
+  </si>
+  <si>
+    <t>carne de peixe</t>
+  </si>
+  <si>
+    <t>carne bovina</t>
+  </si>
+  <si>
+    <t>carne de frango</t>
+  </si>
+  <si>
+    <t>carne suina</t>
+  </si>
+  <si>
+    <t>embutidos</t>
+  </si>
+  <si>
+    <t>composicao</t>
   </si>
 </sst>
 </file>
@@ -1019,15 +1040,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{387CD5D7-9964-4545-A952-8B8C1378E3C8}">
-  <dimension ref="A1:F156"/>
+  <dimension ref="A1:H156"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.54296875" customWidth="1"/>
     <col min="2" max="2" width="16.26953125" customWidth="1"/>
     <col min="4" max="4" width="34.26953125" customWidth="1"/>
+    <col min="5" max="6" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1041,13 +1063,19 @@
         <v>30</v>
       </c>
       <c r="E1" t="s">
+        <v>202</v>
+      </c>
+      <c r="F1" t="s">
+        <v>208</v>
+      </c>
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1057,14 +1085,23 @@
       <c r="C2">
         <v>1</v>
       </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
       <c r="E2" t="s">
         <v>20</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1074,14 +1111,23 @@
       <c r="C3">
         <v>1</v>
       </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
       <c r="E3" t="s">
         <v>20</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1091,14 +1137,23 @@
       <c r="C4">
         <v>1</v>
       </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
       <c r="E4" t="s">
         <v>20</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -1109,16 +1164,22 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
+        <v>203</v>
+      </c>
+      <c r="E5" t="s">
         <v>33</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" t="s">
         <v>19</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -1129,16 +1190,22 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
+        <v>203</v>
+      </c>
+      <c r="E6" t="s">
         <v>33</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" t="s">
         <v>19</v>
       </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -1149,16 +1216,22 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
+        <v>204</v>
+      </c>
+      <c r="E7" t="s">
         <v>29</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" t="s">
         <v>18</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -1169,16 +1242,22 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
+        <v>204</v>
+      </c>
+      <c r="E8" t="s">
         <v>29</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" t="s">
         <v>18</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -1189,16 +1268,22 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
+        <v>204</v>
+      </c>
+      <c r="E9" t="s">
         <v>29</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" t="s">
         <v>18</v>
       </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>46</v>
       </c>
@@ -1209,16 +1294,22 @@
         <v>1</v>
       </c>
       <c r="D10" t="s">
+        <v>204</v>
+      </c>
+      <c r="E10" t="s">
         <v>37</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" t="s">
         <v>18</v>
       </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -1229,16 +1320,22 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
+        <v>204</v>
+      </c>
+      <c r="E11" t="s">
         <v>37</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" t="s">
         <v>18</v>
       </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -1249,16 +1346,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="s">
+        <v>204</v>
+      </c>
+      <c r="E12" t="s">
         <v>37</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" t="s">
         <v>18</v>
       </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1269,16 +1372,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="s">
+        <v>204</v>
+      </c>
+      <c r="E13" t="s">
         <v>24</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" t="s">
         <v>18</v>
       </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1289,16 +1398,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="s">
+        <v>204</v>
+      </c>
+      <c r="E14" t="s">
         <v>42</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" t="s">
         <v>18</v>
       </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -1309,16 +1424,22 @@
         <v>1</v>
       </c>
       <c r="D15" t="s">
+        <v>204</v>
+      </c>
+      <c r="E15" t="s">
         <v>42</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" t="s">
         <v>18</v>
       </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -1329,16 +1450,22 @@
         <v>1</v>
       </c>
       <c r="D16" t="s">
+        <v>204</v>
+      </c>
+      <c r="E16" t="s">
         <v>42</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" t="s">
         <v>18</v>
       </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -1349,16 +1476,22 @@
         <v>1</v>
       </c>
       <c r="D17" t="s">
+        <v>204</v>
+      </c>
+      <c r="E17" t="s">
         <v>42</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" t="s">
         <v>18</v>
       </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -1369,16 +1502,22 @@
         <v>1</v>
       </c>
       <c r="D18" t="s">
+        <v>204</v>
+      </c>
+      <c r="E18" t="s">
         <v>43</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" t="s">
         <v>18</v>
       </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1389,16 +1528,22 @@
         <v>1</v>
       </c>
       <c r="D19" t="s">
+        <v>204</v>
+      </c>
+      <c r="E19" t="s">
         <v>43</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" t="s">
         <v>18</v>
       </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>53</v>
       </c>
@@ -1409,16 +1554,22 @@
         <v>1</v>
       </c>
       <c r="D20" t="s">
+        <v>205</v>
+      </c>
+      <c r="E20" t="s">
         <v>48</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" t="s">
         <v>19</v>
       </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>51</v>
       </c>
@@ -1429,16 +1580,22 @@
         <v>1</v>
       </c>
       <c r="D21" t="s">
+        <v>205</v>
+      </c>
+      <c r="E21" t="s">
         <v>52</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" t="s">
         <v>19</v>
       </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>54</v>
       </c>
@@ -1449,16 +1606,22 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
+        <v>205</v>
+      </c>
+      <c r="E22" t="s">
         <v>50</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" t="s">
         <v>19</v>
       </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -1469,16 +1632,22 @@
         <v>1</v>
       </c>
       <c r="D23" t="s">
+        <v>205</v>
+      </c>
+      <c r="E23" t="s">
         <v>50</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" t="s">
         <v>19</v>
       </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>56</v>
       </c>
@@ -1489,16 +1658,22 @@
         <v>1</v>
       </c>
       <c r="D24" t="s">
+        <v>205</v>
+      </c>
+      <c r="E24" t="s">
         <v>50</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" t="s">
         <v>19</v>
       </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -1509,16 +1684,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="s">
+        <v>205</v>
+      </c>
+      <c r="E25" t="s">
         <v>50</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" t="s">
         <v>19</v>
       </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -1529,16 +1710,22 @@
         <v>1</v>
       </c>
       <c r="D26" t="s">
+        <v>205</v>
+      </c>
+      <c r="E26" t="s">
         <v>50</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
+        <v>20</v>
+      </c>
+      <c r="G26" t="s">
         <v>19</v>
       </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>49</v>
       </c>
@@ -1549,16 +1736,22 @@
         <v>1</v>
       </c>
       <c r="D27" t="s">
+        <v>205</v>
+      </c>
+      <c r="E27" t="s">
         <v>50</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" t="s">
         <v>19</v>
       </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1569,16 +1762,22 @@
         <v>1</v>
       </c>
       <c r="D28" t="s">
+        <v>206</v>
+      </c>
+      <c r="E28" t="s">
         <v>61</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28" t="s">
         <v>18</v>
       </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>59</v>
       </c>
@@ -1589,16 +1788,22 @@
         <v>1</v>
       </c>
       <c r="D29" t="s">
+        <v>206</v>
+      </c>
+      <c r="E29" t="s">
         <v>27</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" t="s">
         <v>18</v>
       </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>60</v>
       </c>
@@ -1609,16 +1814,22 @@
         <v>1</v>
       </c>
       <c r="D30" t="s">
+        <v>206</v>
+      </c>
+      <c r="E30" t="s">
         <v>22</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" t="s">
         <v>18</v>
       </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>62</v>
       </c>
@@ -1629,16 +1840,22 @@
         <v>1</v>
       </c>
       <c r="D31" t="s">
+        <v>207</v>
+      </c>
+      <c r="E31" t="s">
         <v>63</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" t="s">
         <v>18</v>
       </c>
-      <c r="F31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>64</v>
       </c>
@@ -1649,16 +1866,22 @@
         <v>1</v>
       </c>
       <c r="D32" t="s">
+        <v>207</v>
+      </c>
+      <c r="E32" t="s">
         <v>64</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
+        <v>20</v>
+      </c>
+      <c r="G32" t="s">
         <v>18</v>
       </c>
-      <c r="F32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1674,11 +1897,17 @@
       <c r="E33" t="s">
         <v>20</v>
       </c>
-      <c r="F33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F33" t="s">
+        <v>20</v>
+      </c>
+      <c r="G33" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>78</v>
       </c>
@@ -1694,11 +1923,17 @@
       <c r="E34" t="s">
         <v>20</v>
       </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F34" t="s">
+        <v>20</v>
+      </c>
+      <c r="G34" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1714,11 +1949,17 @@
       <c r="E35" t="s">
         <v>20</v>
       </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F35" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35" t="s">
+        <v>20</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>80</v>
       </c>
@@ -1734,11 +1975,17 @@
       <c r="E36" t="s">
         <v>20</v>
       </c>
-      <c r="F36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F36" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>81</v>
       </c>
@@ -1754,11 +2001,17 @@
       <c r="E37" t="s">
         <v>20</v>
       </c>
-      <c r="F37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F37" t="s">
+        <v>20</v>
+      </c>
+      <c r="G37" t="s">
+        <v>20</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>82</v>
       </c>
@@ -1774,11 +2027,17 @@
       <c r="E38" t="s">
         <v>20</v>
       </c>
-      <c r="F38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F38" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38" t="s">
+        <v>20</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>84</v>
       </c>
@@ -1794,11 +2053,17 @@
       <c r="E39" t="s">
         <v>20</v>
       </c>
-      <c r="F39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F39" t="s">
+        <v>20</v>
+      </c>
+      <c r="G39" t="s">
+        <v>20</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>70</v>
       </c>
@@ -1814,11 +2079,17 @@
       <c r="E40" t="s">
         <v>20</v>
       </c>
-      <c r="F40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F40" t="s">
+        <v>20</v>
+      </c>
+      <c r="G40" t="s">
+        <v>20</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>14</v>
       </c>
@@ -1834,11 +2105,17 @@
       <c r="E41" t="s">
         <v>20</v>
       </c>
-      <c r="F41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F41" t="s">
+        <v>20</v>
+      </c>
+      <c r="G41" t="s">
+        <v>20</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>85</v>
       </c>
@@ -1854,11 +2131,17 @@
       <c r="E42" t="s">
         <v>20</v>
       </c>
-      <c r="F42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F42" t="s">
+        <v>20</v>
+      </c>
+      <c r="G42" t="s">
+        <v>20</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>86</v>
       </c>
@@ -1874,11 +2157,17 @@
       <c r="E43" t="s">
         <v>20</v>
       </c>
-      <c r="F43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F43" t="s">
+        <v>20</v>
+      </c>
+      <c r="G43" t="s">
+        <v>20</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>87</v>
       </c>
@@ -1894,11 +2183,17 @@
       <c r="E44" t="s">
         <v>20</v>
       </c>
-      <c r="F44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F44" t="s">
+        <v>20</v>
+      </c>
+      <c r="G44" t="s">
+        <v>20</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>88</v>
       </c>
@@ -1914,11 +2209,17 @@
       <c r="E45" t="s">
         <v>20</v>
       </c>
-      <c r="F45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F45" t="s">
+        <v>20</v>
+      </c>
+      <c r="G45" t="s">
+        <v>20</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>89</v>
       </c>
@@ -1934,11 +2235,17 @@
       <c r="E46" t="s">
         <v>20</v>
       </c>
-      <c r="F46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F46" t="s">
+        <v>20</v>
+      </c>
+      <c r="G46" t="s">
+        <v>20</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>90</v>
       </c>
@@ -1954,11 +2261,17 @@
       <c r="E47" t="s">
         <v>20</v>
       </c>
-      <c r="F47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F47" t="s">
+        <v>20</v>
+      </c>
+      <c r="G47" t="s">
+        <v>20</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>91</v>
       </c>
@@ -1974,11 +2287,17 @@
       <c r="E48" t="s">
         <v>20</v>
       </c>
-      <c r="F48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F48" t="s">
+        <v>20</v>
+      </c>
+      <c r="G48" t="s">
+        <v>20</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>92</v>
       </c>
@@ -1994,11 +2313,17 @@
       <c r="E49" t="s">
         <v>20</v>
       </c>
-      <c r="F49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F49" t="s">
+        <v>20</v>
+      </c>
+      <c r="G49" t="s">
+        <v>20</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>93</v>
       </c>
@@ -2014,11 +2339,17 @@
       <c r="E50" t="s">
         <v>20</v>
       </c>
-      <c r="F50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F50" t="s">
+        <v>20</v>
+      </c>
+      <c r="G50" t="s">
+        <v>20</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>71</v>
       </c>
@@ -2034,11 +2365,17 @@
       <c r="E51" t="s">
         <v>20</v>
       </c>
-      <c r="F51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F51" t="s">
+        <v>20</v>
+      </c>
+      <c r="G51" t="s">
+        <v>20</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>94</v>
       </c>
@@ -2054,11 +2391,17 @@
       <c r="E52" t="s">
         <v>20</v>
       </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F52" t="s">
+        <v>20</v>
+      </c>
+      <c r="G52" t="s">
+        <v>20</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>75</v>
       </c>
@@ -2074,11 +2417,17 @@
       <c r="E53" t="s">
         <v>20</v>
       </c>
-      <c r="F53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F53" t="s">
+        <v>20</v>
+      </c>
+      <c r="G53" t="s">
+        <v>20</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>98</v>
       </c>
@@ -2094,11 +2443,17 @@
       <c r="E54" t="s">
         <v>20</v>
       </c>
-      <c r="F54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F54" t="s">
+        <v>20</v>
+      </c>
+      <c r="G54" t="s">
+        <v>20</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>99</v>
       </c>
@@ -2114,11 +2469,17 @@
       <c r="E55" t="s">
         <v>20</v>
       </c>
-      <c r="F55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F55" t="s">
+        <v>20</v>
+      </c>
+      <c r="G55" t="s">
+        <v>20</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>102</v>
       </c>
@@ -2134,11 +2495,17 @@
       <c r="E56" t="s">
         <v>20</v>
       </c>
-      <c r="F56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F56" t="s">
+        <v>20</v>
+      </c>
+      <c r="G56" t="s">
+        <v>20</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>107</v>
       </c>
@@ -2154,11 +2521,17 @@
       <c r="E57" t="s">
         <v>20</v>
       </c>
-      <c r="F57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F57" t="s">
+        <v>20</v>
+      </c>
+      <c r="G57" t="s">
+        <v>20</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>106</v>
       </c>
@@ -2174,11 +2547,17 @@
       <c r="E58" t="s">
         <v>20</v>
       </c>
-      <c r="F58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F58" t="s">
+        <v>20</v>
+      </c>
+      <c r="G58" t="s">
+        <v>20</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>104</v>
       </c>
@@ -2194,11 +2573,17 @@
       <c r="E59" t="s">
         <v>20</v>
       </c>
-      <c r="F59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F59" t="s">
+        <v>20</v>
+      </c>
+      <c r="G59" t="s">
+        <v>20</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>105</v>
       </c>
@@ -2214,11 +2599,17 @@
       <c r="E60" t="s">
         <v>20</v>
       </c>
-      <c r="F60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F60" t="s">
+        <v>20</v>
+      </c>
+      <c r="G60" t="s">
+        <v>20</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>108</v>
       </c>
@@ -2234,11 +2625,17 @@
       <c r="E61" t="s">
         <v>20</v>
       </c>
-      <c r="F61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F61" t="s">
+        <v>20</v>
+      </c>
+      <c r="G61" t="s">
+        <v>20</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>68</v>
       </c>
@@ -2254,11 +2651,17 @@
       <c r="E62" t="s">
         <v>20</v>
       </c>
-      <c r="F62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F62" t="s">
+        <v>20</v>
+      </c>
+      <c r="G62" t="s">
+        <v>20</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>15</v>
       </c>
@@ -2274,11 +2677,17 @@
       <c r="E63" t="s">
         <v>20</v>
       </c>
-      <c r="F63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F63" t="s">
+        <v>20</v>
+      </c>
+      <c r="G63" t="s">
+        <v>20</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>65</v>
       </c>
@@ -2294,11 +2703,17 @@
       <c r="E64" t="s">
         <v>20</v>
       </c>
-      <c r="F64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F64" t="s">
+        <v>20</v>
+      </c>
+      <c r="G64" t="s">
+        <v>20</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>95</v>
       </c>
@@ -2314,11 +2729,17 @@
       <c r="E65" t="s">
         <v>20</v>
       </c>
-      <c r="F65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F65" t="s">
+        <v>20</v>
+      </c>
+      <c r="G65" t="s">
+        <v>20</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>96</v>
       </c>
@@ -2334,11 +2755,17 @@
       <c r="E66" t="s">
         <v>20</v>
       </c>
-      <c r="F66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F66" t="s">
+        <v>20</v>
+      </c>
+      <c r="G66" t="s">
+        <v>20</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>77</v>
       </c>
@@ -2354,11 +2781,17 @@
       <c r="E67" t="s">
         <v>20</v>
       </c>
-      <c r="F67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F67" t="s">
+        <v>20</v>
+      </c>
+      <c r="G67" t="s">
+        <v>20</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>73</v>
       </c>
@@ -2374,11 +2807,17 @@
       <c r="E68" t="s">
         <v>20</v>
       </c>
-      <c r="F68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F68" t="s">
+        <v>20</v>
+      </c>
+      <c r="G68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>101</v>
       </c>
@@ -2394,11 +2833,17 @@
       <c r="E69" t="s">
         <v>20</v>
       </c>
-      <c r="F69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F69" t="s">
+        <v>20</v>
+      </c>
+      <c r="G69" t="s">
+        <v>20</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>110</v>
       </c>
@@ -2409,16 +2854,22 @@
         <v>1</v>
       </c>
       <c r="D70" t="s">
+        <v>20</v>
+      </c>
+      <c r="E70" t="s">
+        <v>20</v>
+      </c>
+      <c r="F70" t="s">
         <v>137</v>
       </c>
-      <c r="E70" t="s">
-        <v>20</v>
-      </c>
-      <c r="F70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G70" t="s">
+        <v>20</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>111</v>
       </c>
@@ -2429,16 +2880,22 @@
         <v>1</v>
       </c>
       <c r="D71" t="s">
+        <v>20</v>
+      </c>
+      <c r="E71" t="s">
+        <v>20</v>
+      </c>
+      <c r="F71" t="s">
         <v>138</v>
       </c>
-      <c r="E71" t="s">
-        <v>20</v>
-      </c>
-      <c r="F71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G71" t="s">
+        <v>20</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>112</v>
       </c>
@@ -2449,16 +2906,22 @@
         <v>1</v>
       </c>
       <c r="D72" t="s">
+        <v>20</v>
+      </c>
+      <c r="E72" t="s">
+        <v>20</v>
+      </c>
+      <c r="F72" t="s">
         <v>139</v>
       </c>
-      <c r="E72" t="s">
-        <v>20</v>
-      </c>
-      <c r="F72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G72" t="s">
+        <v>20</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>72</v>
       </c>
@@ -2469,16 +2932,22 @@
         <v>1</v>
       </c>
       <c r="D73" t="s">
+        <v>20</v>
+      </c>
+      <c r="E73" t="s">
+        <v>20</v>
+      </c>
+      <c r="F73" t="s">
         <v>143</v>
       </c>
-      <c r="E73" t="s">
-        <v>20</v>
-      </c>
-      <c r="F73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G73" t="s">
+        <v>20</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>113</v>
       </c>
@@ -2489,16 +2958,22 @@
         <v>1</v>
       </c>
       <c r="D74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E74" t="s">
+        <v>20</v>
+      </c>
+      <c r="F74" t="s">
         <v>140</v>
       </c>
-      <c r="E74" t="s">
-        <v>20</v>
-      </c>
-      <c r="F74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G74" t="s">
+        <v>20</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>114</v>
       </c>
@@ -2509,16 +2984,22 @@
         <v>1</v>
       </c>
       <c r="D75" t="s">
+        <v>20</v>
+      </c>
+      <c r="E75" t="s">
+        <v>20</v>
+      </c>
+      <c r="F75" t="s">
         <v>140</v>
       </c>
-      <c r="E75" t="s">
-        <v>20</v>
-      </c>
-      <c r="F75">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>115</v>
       </c>
@@ -2529,16 +3010,22 @@
         <v>1</v>
       </c>
       <c r="D76" t="s">
+        <v>20</v>
+      </c>
+      <c r="E76" t="s">
+        <v>20</v>
+      </c>
+      <c r="F76" t="s">
         <v>140</v>
       </c>
-      <c r="E76" t="s">
-        <v>20</v>
-      </c>
-      <c r="F76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G76" t="s">
+        <v>20</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>116</v>
       </c>
@@ -2549,16 +3036,22 @@
         <v>1</v>
       </c>
       <c r="D77" t="s">
+        <v>20</v>
+      </c>
+      <c r="E77" t="s">
+        <v>20</v>
+      </c>
+      <c r="F77" t="s">
         <v>140</v>
       </c>
-      <c r="E77" t="s">
-        <v>20</v>
-      </c>
-      <c r="F77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G77" t="s">
+        <v>20</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>117</v>
       </c>
@@ -2569,16 +3062,22 @@
         <v>1</v>
       </c>
       <c r="D78" t="s">
+        <v>20</v>
+      </c>
+      <c r="E78" t="s">
+        <v>20</v>
+      </c>
+      <c r="F78" t="s">
         <v>143</v>
       </c>
-      <c r="E78" t="s">
-        <v>20</v>
-      </c>
-      <c r="F78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G78" t="s">
+        <v>20</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>17</v>
       </c>
@@ -2589,16 +3088,22 @@
         <v>1</v>
       </c>
       <c r="D79" t="s">
+        <v>20</v>
+      </c>
+      <c r="E79" t="s">
+        <v>20</v>
+      </c>
+      <c r="F79" t="s">
         <v>142</v>
       </c>
-      <c r="E79" t="s">
-        <v>20</v>
-      </c>
-      <c r="F79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G79" t="s">
+        <v>20</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>118</v>
       </c>
@@ -2609,16 +3114,22 @@
         <v>1</v>
       </c>
       <c r="D80" t="s">
+        <v>20</v>
+      </c>
+      <c r="E80" t="s">
+        <v>20</v>
+      </c>
+      <c r="F80" t="s">
         <v>143</v>
       </c>
-      <c r="E80" t="s">
-        <v>20</v>
-      </c>
-      <c r="F80">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G80" t="s">
+        <v>20</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>119</v>
       </c>
@@ -2629,16 +3140,22 @@
         <v>1</v>
       </c>
       <c r="D81" t="s">
+        <v>20</v>
+      </c>
+      <c r="E81" t="s">
+        <v>20</v>
+      </c>
+      <c r="F81" t="s">
         <v>141</v>
       </c>
-      <c r="E81" t="s">
-        <v>20</v>
-      </c>
-      <c r="F81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G81" t="s">
+        <v>20</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>121</v>
       </c>
@@ -2649,16 +3166,22 @@
         <v>1</v>
       </c>
       <c r="D82" t="s">
+        <v>20</v>
+      </c>
+      <c r="E82" t="s">
+        <v>20</v>
+      </c>
+      <c r="F82" t="s">
         <v>143</v>
       </c>
-      <c r="E82" t="s">
-        <v>20</v>
-      </c>
-      <c r="F82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G82" t="s">
+        <v>20</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>122</v>
       </c>
@@ -2669,16 +3192,22 @@
         <v>1</v>
       </c>
       <c r="D83" t="s">
+        <v>20</v>
+      </c>
+      <c r="E83" t="s">
+        <v>20</v>
+      </c>
+      <c r="F83" t="s">
         <v>141</v>
       </c>
-      <c r="E83" t="s">
-        <v>20</v>
-      </c>
-      <c r="F83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G83" t="s">
+        <v>20</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>123</v>
       </c>
@@ -2689,16 +3218,22 @@
         <v>1</v>
       </c>
       <c r="D84" t="s">
+        <v>20</v>
+      </c>
+      <c r="E84" t="s">
+        <v>20</v>
+      </c>
+      <c r="F84" t="s">
         <v>143</v>
       </c>
-      <c r="E84" t="s">
-        <v>20</v>
-      </c>
-      <c r="F84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G84" t="s">
+        <v>20</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>120</v>
       </c>
@@ -2709,16 +3244,22 @@
         <v>1</v>
       </c>
       <c r="D85" t="s">
+        <v>20</v>
+      </c>
+      <c r="E85" t="s">
+        <v>20</v>
+      </c>
+      <c r="F85" t="s">
         <v>143</v>
       </c>
-      <c r="E85" t="s">
-        <v>20</v>
-      </c>
-      <c r="F85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G85" t="s">
+        <v>20</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>124</v>
       </c>
@@ -2729,16 +3270,22 @@
         <v>1</v>
       </c>
       <c r="D86" t="s">
+        <v>20</v>
+      </c>
+      <c r="E86" t="s">
+        <v>20</v>
+      </c>
+      <c r="F86" t="s">
         <v>140</v>
       </c>
-      <c r="E86" t="s">
-        <v>20</v>
-      </c>
-      <c r="F86">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G86" t="s">
+        <v>20</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>125</v>
       </c>
@@ -2749,16 +3296,22 @@
         <v>1</v>
       </c>
       <c r="D87" t="s">
+        <v>20</v>
+      </c>
+      <c r="E87" t="s">
+        <v>20</v>
+      </c>
+      <c r="F87" t="s">
         <v>140</v>
       </c>
-      <c r="E87" t="s">
-        <v>20</v>
-      </c>
-      <c r="F87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G87" t="s">
+        <v>20</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>126</v>
       </c>
@@ -2769,16 +3322,22 @@
         <v>1</v>
       </c>
       <c r="D88" t="s">
+        <v>20</v>
+      </c>
+      <c r="E88" t="s">
+        <v>20</v>
+      </c>
+      <c r="F88" t="s">
         <v>143</v>
       </c>
-      <c r="E88" t="s">
-        <v>20</v>
-      </c>
-      <c r="F88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G88" t="s">
+        <v>20</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>127</v>
       </c>
@@ -2789,16 +3348,22 @@
         <v>1</v>
       </c>
       <c r="D89" t="s">
+        <v>20</v>
+      </c>
+      <c r="E89" t="s">
+        <v>20</v>
+      </c>
+      <c r="F89" t="s">
         <v>143</v>
       </c>
-      <c r="E89" t="s">
-        <v>20</v>
-      </c>
-      <c r="F89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G89" t="s">
+        <v>20</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>128</v>
       </c>
@@ -2809,16 +3374,22 @@
         <v>1</v>
       </c>
       <c r="D90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E90" t="s">
+        <v>20</v>
+      </c>
+      <c r="F90" t="s">
         <v>143</v>
       </c>
-      <c r="E90" t="s">
-        <v>20</v>
-      </c>
-      <c r="F90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G90" t="s">
+        <v>20</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>129</v>
       </c>
@@ -2829,16 +3400,22 @@
         <v>1</v>
       </c>
       <c r="D91" t="s">
+        <v>20</v>
+      </c>
+      <c r="E91" t="s">
+        <v>20</v>
+      </c>
+      <c r="F91" t="s">
         <v>140</v>
       </c>
-      <c r="E91" t="s">
-        <v>20</v>
-      </c>
-      <c r="F91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G91" t="s">
+        <v>20</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>130</v>
       </c>
@@ -2849,16 +3426,22 @@
         <v>1</v>
       </c>
       <c r="D92" t="s">
+        <v>20</v>
+      </c>
+      <c r="E92" t="s">
+        <v>20</v>
+      </c>
+      <c r="F92" t="s">
         <v>140</v>
       </c>
-      <c r="E92" t="s">
-        <v>20</v>
-      </c>
-      <c r="F92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G92" t="s">
+        <v>20</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>131</v>
       </c>
@@ -2869,16 +3452,22 @@
         <v>1</v>
       </c>
       <c r="D93" t="s">
+        <v>20</v>
+      </c>
+      <c r="E93" t="s">
+        <v>20</v>
+      </c>
+      <c r="F93" t="s">
         <v>141</v>
       </c>
-      <c r="E93" t="s">
-        <v>20</v>
-      </c>
-      <c r="F93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G93" t="s">
+        <v>20</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>132</v>
       </c>
@@ -2889,16 +3478,22 @@
         <v>1</v>
       </c>
       <c r="D94" t="s">
+        <v>20</v>
+      </c>
+      <c r="E94" t="s">
+        <v>20</v>
+      </c>
+      <c r="F94" t="s">
         <v>143</v>
       </c>
-      <c r="E94" t="s">
-        <v>20</v>
-      </c>
-      <c r="F94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G94" t="s">
+        <v>20</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>133</v>
       </c>
@@ -2909,16 +3504,22 @@
         <v>1</v>
       </c>
       <c r="D95" t="s">
+        <v>20</v>
+      </c>
+      <c r="E95" t="s">
+        <v>20</v>
+      </c>
+      <c r="F95" t="s">
         <v>144</v>
       </c>
-      <c r="E95" t="s">
-        <v>20</v>
-      </c>
-      <c r="F95">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G95" t="s">
+        <v>20</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>134</v>
       </c>
@@ -2929,16 +3530,22 @@
         <v>1</v>
       </c>
       <c r="D96" t="s">
+        <v>20</v>
+      </c>
+      <c r="E96" t="s">
+        <v>20</v>
+      </c>
+      <c r="F96" t="s">
         <v>138</v>
       </c>
-      <c r="E96" t="s">
-        <v>20</v>
-      </c>
-      <c r="F96">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G96" t="s">
+        <v>20</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>135</v>
       </c>
@@ -2949,16 +3556,22 @@
         <v>1</v>
       </c>
       <c r="D97" t="s">
+        <v>20</v>
+      </c>
+      <c r="E97" t="s">
+        <v>20</v>
+      </c>
+      <c r="F97" t="s">
         <v>141</v>
       </c>
-      <c r="E97" t="s">
-        <v>20</v>
-      </c>
-      <c r="F97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G97" t="s">
+        <v>20</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>5</v>
       </c>
@@ -2974,11 +3587,17 @@
       <c r="E98" t="s">
         <v>20</v>
       </c>
-      <c r="F98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F98" t="s">
+        <v>20</v>
+      </c>
+      <c r="G98" t="s">
+        <v>20</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>145</v>
       </c>
@@ -2994,11 +3613,17 @@
       <c r="E99" t="s">
         <v>20</v>
       </c>
-      <c r="F99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F99" t="s">
+        <v>20</v>
+      </c>
+      <c r="G99" t="s">
+        <v>20</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>146</v>
       </c>
@@ -3014,11 +3639,17 @@
       <c r="E100" t="s">
         <v>20</v>
       </c>
-      <c r="F100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F100" t="s">
+        <v>20</v>
+      </c>
+      <c r="G100" t="s">
+        <v>20</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>147</v>
       </c>
@@ -3034,11 +3665,17 @@
       <c r="E101" t="s">
         <v>20</v>
       </c>
-      <c r="F101">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F101" t="s">
+        <v>20</v>
+      </c>
+      <c r="G101" t="s">
+        <v>20</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>148</v>
       </c>
@@ -3054,11 +3691,17 @@
       <c r="E102" t="s">
         <v>20</v>
       </c>
-      <c r="F102">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F102" t="s">
+        <v>20</v>
+      </c>
+      <c r="G102" t="s">
+        <v>20</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>149</v>
       </c>
@@ -3074,11 +3717,17 @@
       <c r="E103" t="s">
         <v>20</v>
       </c>
-      <c r="F103">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F103" t="s">
+        <v>20</v>
+      </c>
+      <c r="G103" t="s">
+        <v>20</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>150</v>
       </c>
@@ -3094,11 +3743,17 @@
       <c r="E104" t="s">
         <v>20</v>
       </c>
-      <c r="F104">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F104" t="s">
+        <v>20</v>
+      </c>
+      <c r="G104" t="s">
+        <v>20</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>151</v>
       </c>
@@ -3114,11 +3769,17 @@
       <c r="E105" t="s">
         <v>20</v>
       </c>
-      <c r="F105">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F105" t="s">
+        <v>20</v>
+      </c>
+      <c r="G105" t="s">
+        <v>20</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>152</v>
       </c>
@@ -3134,11 +3795,17 @@
       <c r="E106" t="s">
         <v>20</v>
       </c>
-      <c r="F106">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F106" t="s">
+        <v>20</v>
+      </c>
+      <c r="G106" t="s">
+        <v>20</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>153</v>
       </c>
@@ -3154,11 +3821,17 @@
       <c r="E107" t="s">
         <v>20</v>
       </c>
-      <c r="F107">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F107" t="s">
+        <v>20</v>
+      </c>
+      <c r="G107" t="s">
+        <v>20</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>154</v>
       </c>
@@ -3174,11 +3847,17 @@
       <c r="E108" t="s">
         <v>20</v>
       </c>
-      <c r="F108">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F108" t="s">
+        <v>20</v>
+      </c>
+      <c r="G108" t="s">
+        <v>20</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>155</v>
       </c>
@@ -3194,11 +3873,17 @@
       <c r="E109" t="s">
         <v>20</v>
       </c>
-      <c r="F109">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F109" t="s">
+        <v>20</v>
+      </c>
+      <c r="G109" t="s">
+        <v>20</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>156</v>
       </c>
@@ -3214,11 +3899,17 @@
       <c r="E110" t="s">
         <v>20</v>
       </c>
-      <c r="F110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F110" t="s">
+        <v>20</v>
+      </c>
+      <c r="G110" t="s">
+        <v>20</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>157</v>
       </c>
@@ -3234,11 +3925,17 @@
       <c r="E111" t="s">
         <v>20</v>
       </c>
-      <c r="F111">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F111" t="s">
+        <v>20</v>
+      </c>
+      <c r="G111" t="s">
+        <v>20</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>158</v>
       </c>
@@ -3254,11 +3951,17 @@
       <c r="E112" t="s">
         <v>20</v>
       </c>
-      <c r="F112">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F112" t="s">
+        <v>20</v>
+      </c>
+      <c r="G112" t="s">
+        <v>20</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>159</v>
       </c>
@@ -3274,11 +3977,17 @@
       <c r="E113" t="s">
         <v>20</v>
       </c>
-      <c r="F113">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F113" t="s">
+        <v>20</v>
+      </c>
+      <c r="G113" t="s">
+        <v>20</v>
+      </c>
+      <c r="H113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>160</v>
       </c>
@@ -3294,11 +4003,17 @@
       <c r="E114" t="s">
         <v>20</v>
       </c>
-      <c r="F114">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F114" t="s">
+        <v>20</v>
+      </c>
+      <c r="G114" t="s">
+        <v>20</v>
+      </c>
+      <c r="H114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>161</v>
       </c>
@@ -3314,11 +4029,17 @@
       <c r="E115" t="s">
         <v>20</v>
       </c>
-      <c r="F115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F115" t="s">
+        <v>20</v>
+      </c>
+      <c r="G115" t="s">
+        <v>20</v>
+      </c>
+      <c r="H115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>162</v>
       </c>
@@ -3334,11 +4055,17 @@
       <c r="E116" t="s">
         <v>20</v>
       </c>
-      <c r="F116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F116" t="s">
+        <v>20</v>
+      </c>
+      <c r="G116" t="s">
+        <v>20</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>163</v>
       </c>
@@ -3354,11 +4081,17 @@
       <c r="E117" t="s">
         <v>20</v>
       </c>
-      <c r="F117">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F117" t="s">
+        <v>20</v>
+      </c>
+      <c r="G117" t="s">
+        <v>20</v>
+      </c>
+      <c r="H117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>164</v>
       </c>
@@ -3374,11 +4107,17 @@
       <c r="E118" t="s">
         <v>20</v>
       </c>
-      <c r="F118">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F118" t="s">
+        <v>20</v>
+      </c>
+      <c r="G118" t="s">
+        <v>20</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>165</v>
       </c>
@@ -3394,11 +4133,17 @@
       <c r="E119" t="s">
         <v>20</v>
       </c>
-      <c r="F119">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F119" t="s">
+        <v>20</v>
+      </c>
+      <c r="G119" t="s">
+        <v>20</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>166</v>
       </c>
@@ -3414,11 +4159,17 @@
       <c r="E120" t="s">
         <v>20</v>
       </c>
-      <c r="F120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F120" t="s">
+        <v>20</v>
+      </c>
+      <c r="G120" t="s">
+        <v>20</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>167</v>
       </c>
@@ -3434,11 +4185,17 @@
       <c r="E121" t="s">
         <v>20</v>
       </c>
-      <c r="F121">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F121" t="s">
+        <v>20</v>
+      </c>
+      <c r="G121" t="s">
+        <v>20</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>168</v>
       </c>
@@ -3454,11 +4211,17 @@
       <c r="E122" t="s">
         <v>20</v>
       </c>
-      <c r="F122">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F122" t="s">
+        <v>20</v>
+      </c>
+      <c r="G122" t="s">
+        <v>20</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>169</v>
       </c>
@@ -3474,11 +4237,17 @@
       <c r="E123" t="s">
         <v>20</v>
       </c>
-      <c r="F123">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F123" t="s">
+        <v>20</v>
+      </c>
+      <c r="G123" t="s">
+        <v>20</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>170</v>
       </c>
@@ -3494,11 +4263,17 @@
       <c r="E124" t="s">
         <v>20</v>
       </c>
-      <c r="F124">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F124" t="s">
+        <v>20</v>
+      </c>
+      <c r="G124" t="s">
+        <v>20</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>171</v>
       </c>
@@ -3514,11 +4289,17 @@
       <c r="E125" t="s">
         <v>20</v>
       </c>
-      <c r="F125">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F125" t="s">
+        <v>20</v>
+      </c>
+      <c r="G125" t="s">
+        <v>20</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>172</v>
       </c>
@@ -3534,11 +4315,17 @@
       <c r="E126" t="s">
         <v>20</v>
       </c>
-      <c r="F126">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F126" t="s">
+        <v>20</v>
+      </c>
+      <c r="G126" t="s">
+        <v>20</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>173</v>
       </c>
@@ -3554,11 +4341,17 @@
       <c r="E127" t="s">
         <v>20</v>
       </c>
-      <c r="F127">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F127" t="s">
+        <v>20</v>
+      </c>
+      <c r="G127" t="s">
+        <v>20</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>174</v>
       </c>
@@ -3574,11 +4367,17 @@
       <c r="E128" t="s">
         <v>20</v>
       </c>
-      <c r="F128">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F128" t="s">
+        <v>20</v>
+      </c>
+      <c r="G128" t="s">
+        <v>20</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>175</v>
       </c>
@@ -3594,11 +4393,17 @@
       <c r="E129" t="s">
         <v>20</v>
       </c>
-      <c r="F129">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F129" t="s">
+        <v>20</v>
+      </c>
+      <c r="G129" t="s">
+        <v>20</v>
+      </c>
+      <c r="H129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>176</v>
       </c>
@@ -3614,11 +4419,17 @@
       <c r="E130" t="s">
         <v>20</v>
       </c>
-      <c r="F130">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F130" t="s">
+        <v>20</v>
+      </c>
+      <c r="G130" t="s">
+        <v>20</v>
+      </c>
+      <c r="H130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>192</v>
       </c>
@@ -3634,11 +4445,17 @@
       <c r="E131" t="s">
         <v>20</v>
       </c>
-      <c r="F131">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F131" t="s">
+        <v>20</v>
+      </c>
+      <c r="G131" t="s">
+        <v>20</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>177</v>
       </c>
@@ -3654,11 +4471,17 @@
       <c r="E132" t="s">
         <v>20</v>
       </c>
-      <c r="F132">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F132" t="s">
+        <v>20</v>
+      </c>
+      <c r="G132" t="s">
+        <v>20</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>178</v>
       </c>
@@ -3674,11 +4497,17 @@
       <c r="E133" t="s">
         <v>20</v>
       </c>
-      <c r="F133">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F133" t="s">
+        <v>20</v>
+      </c>
+      <c r="G133" t="s">
+        <v>20</v>
+      </c>
+      <c r="H133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>179</v>
       </c>
@@ -3694,11 +4523,17 @@
       <c r="E134" t="s">
         <v>20</v>
       </c>
-      <c r="F134">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F134" t="s">
+        <v>20</v>
+      </c>
+      <c r="G134" t="s">
+        <v>20</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>180</v>
       </c>
@@ -3714,11 +4549,17 @@
       <c r="E135" t="s">
         <v>20</v>
       </c>
-      <c r="F135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F135" t="s">
+        <v>20</v>
+      </c>
+      <c r="G135" t="s">
+        <v>20</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>181</v>
       </c>
@@ -3734,11 +4575,17 @@
       <c r="E136" t="s">
         <v>20</v>
       </c>
-      <c r="F136">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F136" t="s">
+        <v>20</v>
+      </c>
+      <c r="G136" t="s">
+        <v>20</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>182</v>
       </c>
@@ -3754,11 +4601,17 @@
       <c r="E137" t="s">
         <v>20</v>
       </c>
-      <c r="F137">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F137" t="s">
+        <v>20</v>
+      </c>
+      <c r="G137" t="s">
+        <v>20</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>183</v>
       </c>
@@ -3774,11 +4627,17 @@
       <c r="E138" t="s">
         <v>20</v>
       </c>
-      <c r="F138">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F138" t="s">
+        <v>20</v>
+      </c>
+      <c r="G138" t="s">
+        <v>20</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>184</v>
       </c>
@@ -3794,11 +4653,17 @@
       <c r="E139" t="s">
         <v>20</v>
       </c>
-      <c r="F139">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F139" t="s">
+        <v>20</v>
+      </c>
+      <c r="G139" t="s">
+        <v>20</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>185</v>
       </c>
@@ -3814,11 +4679,17 @@
       <c r="E140" t="s">
         <v>20</v>
       </c>
-      <c r="F140">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F140" t="s">
+        <v>20</v>
+      </c>
+      <c r="G140" t="s">
+        <v>20</v>
+      </c>
+      <c r="H140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>186</v>
       </c>
@@ -3834,11 +4705,17 @@
       <c r="E141" t="s">
         <v>20</v>
       </c>
-      <c r="F141">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F141" t="s">
+        <v>20</v>
+      </c>
+      <c r="G141" t="s">
+        <v>20</v>
+      </c>
+      <c r="H141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>187</v>
       </c>
@@ -3854,11 +4731,17 @@
       <c r="E142" t="s">
         <v>20</v>
       </c>
-      <c r="F142">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F142" t="s">
+        <v>20</v>
+      </c>
+      <c r="G142" t="s">
+        <v>20</v>
+      </c>
+      <c r="H142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>188</v>
       </c>
@@ -3874,11 +4757,17 @@
       <c r="E143" t="s">
         <v>20</v>
       </c>
-      <c r="F143">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F143" t="s">
+        <v>20</v>
+      </c>
+      <c r="G143" t="s">
+        <v>20</v>
+      </c>
+      <c r="H143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>189</v>
       </c>
@@ -3894,11 +4783,17 @@
       <c r="E144" t="s">
         <v>20</v>
       </c>
-      <c r="F144">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F144" t="s">
+        <v>20</v>
+      </c>
+      <c r="G144" t="s">
+        <v>20</v>
+      </c>
+      <c r="H144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>190</v>
       </c>
@@ -3914,11 +4809,17 @@
       <c r="E145" t="s">
         <v>20</v>
       </c>
-      <c r="F145">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F145" t="s">
+        <v>20</v>
+      </c>
+      <c r="G145" t="s">
+        <v>20</v>
+      </c>
+      <c r="H145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>191</v>
       </c>
@@ -3934,11 +4835,17 @@
       <c r="E146" t="s">
         <v>20</v>
       </c>
-      <c r="F146">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F146" t="s">
+        <v>20</v>
+      </c>
+      <c r="G146" t="s">
+        <v>20</v>
+      </c>
+      <c r="H146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>193</v>
       </c>
@@ -3954,11 +4861,17 @@
       <c r="E147" t="s">
         <v>20</v>
       </c>
-      <c r="F147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F147" t="s">
+        <v>20</v>
+      </c>
+      <c r="G147" t="s">
+        <v>20</v>
+      </c>
+      <c r="H147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>28</v>
       </c>
@@ -3974,11 +4887,17 @@
       <c r="E148" t="s">
         <v>20</v>
       </c>
-      <c r="F148">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F148" t="s">
+        <v>20</v>
+      </c>
+      <c r="G148" t="s">
+        <v>20</v>
+      </c>
+      <c r="H148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>194</v>
       </c>
@@ -3994,11 +4913,17 @@
       <c r="E149" t="s">
         <v>20</v>
       </c>
-      <c r="F149">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F149" t="s">
+        <v>20</v>
+      </c>
+      <c r="G149" t="s">
+        <v>20</v>
+      </c>
+      <c r="H149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>195</v>
       </c>
@@ -4014,11 +4939,17 @@
       <c r="E150" t="s">
         <v>20</v>
       </c>
-      <c r="F150">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F150" t="s">
+        <v>20</v>
+      </c>
+      <c r="G150" t="s">
+        <v>20</v>
+      </c>
+      <c r="H150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>196</v>
       </c>
@@ -4034,11 +4965,17 @@
       <c r="E151" t="s">
         <v>20</v>
       </c>
-      <c r="F151">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F151" t="s">
+        <v>20</v>
+      </c>
+      <c r="G151" t="s">
+        <v>20</v>
+      </c>
+      <c r="H151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>197</v>
       </c>
@@ -4054,11 +4991,17 @@
       <c r="E152" t="s">
         <v>20</v>
       </c>
-      <c r="F152">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F152" t="s">
+        <v>20</v>
+      </c>
+      <c r="G152" t="s">
+        <v>20</v>
+      </c>
+      <c r="H152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>198</v>
       </c>
@@ -4074,11 +5017,17 @@
       <c r="E153" t="s">
         <v>20</v>
       </c>
-      <c r="F153">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F153" t="s">
+        <v>20</v>
+      </c>
+      <c r="G153" t="s">
+        <v>20</v>
+      </c>
+      <c r="H153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>199</v>
       </c>
@@ -4094,11 +5043,17 @@
       <c r="E154" t="s">
         <v>20</v>
       </c>
-      <c r="F154">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F154" t="s">
+        <v>20</v>
+      </c>
+      <c r="G154" t="s">
+        <v>20</v>
+      </c>
+      <c r="H154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>200</v>
       </c>
@@ -4114,11 +5069,17 @@
       <c r="E155" t="s">
         <v>20</v>
       </c>
-      <c r="F155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F155" t="s">
+        <v>20</v>
+      </c>
+      <c r="G155" t="s">
+        <v>20</v>
+      </c>
+      <c r="H155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>201</v>
       </c>
@@ -4134,7 +5095,13 @@
       <c r="E156" t="s">
         <v>20</v>
       </c>
-      <c r="F156">
+      <c r="F156" t="s">
+        <v>20</v>
+      </c>
+      <c r="G156" t="s">
+        <v>20</v>
+      </c>
+      <c r="H156">
         <v>0</v>
       </c>
     </row>
